--- a/Sheets/SimulataneousFitResultsThesis.xlsx
+++ b/Sheets/SimulataneousFitResultsThesis.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samuelgrant/Documents/gm2/EDM/Sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C6C4270-6D10-C943-8D16-072281B2F8FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE2A1F3-F7BD-D243-B399-37F7F3C128A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="500" windowWidth="23580" windowHeight="16940" xr2:uid="{17D71C46-F216-1347-8A90-14C7EE0E0845}"/>
+    <workbookView xWindow="60" yWindow="500" windowWidth="23580" windowHeight="16940" activeTab="1" xr2:uid="{17D71C46-F216-1347-8A90-14C7EE0E0845}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="SimultaneousFits" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="26">
   <si>
     <t>d_EDM</t>
   </si>
@@ -104,6 +105,15 @@
   </si>
   <si>
     <t>MINUS PHI ERR</t>
+  </si>
+  <si>
+    <t>A_EDM [mrad]</t>
+  </si>
+  <si>
+    <t>delta lab [rmad]</t>
+  </si>
+  <si>
+    <t>d_EDM (S12S18)</t>
   </si>
 </sst>
 </file>
@@ -112,11 +122,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.0000000"/>
-    <numFmt numFmtId="167" formatCode="0.00000000"/>
-    <numFmt numFmtId="168" formatCode="0.00000"/>
-    <numFmt numFmtId="169" formatCode="0.0E+00"/>
-    <numFmt numFmtId="170" formatCode="0.000000000000"/>
+    <numFmt numFmtId="165" formatCode="0.0000000"/>
+    <numFmt numFmtId="166" formatCode="0.00000000"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
+    <numFmt numFmtId="168" formatCode="0.0E+00"/>
+    <numFmt numFmtId="169" formatCode="0.000000000000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -147,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -155,11 +165,14 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -481,7 +494,9 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.33203125" bestFit="1" customWidth="1"/>
@@ -509,28 +524,28 @@
       <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10" t="s">
+      <c r="C4" s="11"/>
+      <c r="D4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="10"/>
+      <c r="E4" s="11"/>
       <c r="F4" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -559,11 +574,11 @@
       <c r="C6">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="7">
         <f>B6/$A$2</f>
         <v>0.41333333333333333</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="7">
         <f>D6*SQRT((C6/B6)^2+($B$2/$A$2)^2)</f>
         <v>8.2981669848612938E-2</v>
       </c>
@@ -586,11 +601,11 @@
       <c r="C7">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="7">
         <f t="shared" ref="D7:D8" si="0">B7/$A$2</f>
         <v>0.37333333333333335</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="7">
         <f t="shared" ref="E7:E9" si="1">D7*SQRT((C7/B7)^2+($B$2/$A$2)^2)</f>
         <v>6.9576553451025855E-2</v>
       </c>
@@ -613,11 +628,11 @@
       <c r="C8">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="7">
         <f t="shared" si="0"/>
         <v>0.6133333333333334</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="7">
         <f t="shared" si="1"/>
         <v>6.2565655391499747E-2</v>
       </c>
@@ -640,11 +655,11 @@
       <c r="C9">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="7">
         <f>B9/$A$2</f>
         <v>0.44000000000000006</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="7">
         <f t="shared" si="1"/>
         <v>5.8267734543990042E-2</v>
       </c>
@@ -661,14 +676,14 @@
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10" t="s">
+      <c r="C11" s="11"/>
+      <c r="D11" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="10"/>
+      <c r="E11" s="11"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -697,11 +712,11 @@
       <c r="C13">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="7">
         <f>B13/$A$2</f>
         <v>0.58666666666666667</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="7">
         <f>D13*SQRT((C13/B13)^2+($B$2/$A$2)^2)</f>
         <v>0.12401207428271342</v>
       </c>
@@ -722,11 +737,11 @@
       <c r="C14">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="7">
         <f t="shared" ref="D14:D15" si="2">B14/$A$2</f>
         <v>0.34666666666666668</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="7">
         <f t="shared" ref="E14:E16" si="3">D14*SQRT((C14/B14)^2+($B$2/$A$2)^2)</f>
         <v>0.10825717893111504</v>
       </c>
@@ -747,11 +762,11 @@
       <c r="C15">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="7">
         <f t="shared" si="2"/>
         <v>0.64</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="7">
         <f t="shared" si="3"/>
         <v>8.6977493896090427E-2</v>
       </c>
@@ -772,11 +787,11 @@
       <c r="C16">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="7">
         <f>B16/$A$2</f>
         <v>0.46666666666666673</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="7">
         <f t="shared" si="3"/>
         <v>7.1161093545334897E-2</v>
       </c>
@@ -791,14 +806,14 @@
       <c r="A18" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10" t="s">
+      <c r="C18" s="11"/>
+      <c r="D18" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="10"/>
+      <c r="E18" s="11"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
@@ -827,11 +842,11 @@
       <c r="C20">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="7">
         <f>B20/$A$2</f>
         <v>0.22666666666666668</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="7">
         <f>D20*SQRT((C20/B20)^2+($B$2/$A$2)^2)</f>
         <v>0.12060738466017699</v>
       </c>
@@ -852,11 +867,11 @@
       <c r="C21">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="7">
         <f t="shared" ref="D21:D22" si="4">B21/$A$2</f>
         <v>0.41333333333333333</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="7">
         <f t="shared" ref="E21:E23" si="5">D21*SQRT((C21/B21)^2+($B$2/$A$2)^2)</f>
         <v>0.1089207753766102</v>
       </c>
@@ -877,11 +892,11 @@
       <c r="C22">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="7">
         <f t="shared" si="4"/>
         <v>0.58666666666666667</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="7">
         <f t="shared" si="5"/>
         <v>9.8438334397796215E-2</v>
       </c>
@@ -902,11 +917,11 @@
       <c r="C23">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="7">
         <f>B23/$A$2</f>
         <v>0.41333333333333333</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="7">
         <f t="shared" si="5"/>
         <v>8.2981669848612938E-2</v>
       </c>
@@ -932,20 +947,20 @@
       <c r="A27" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D27" s="10"/>
+      <c r="D27" s="11"/>
       <c r="F27" t="s">
         <v>10</v>
       </c>
       <c r="G27" t="s">
         <v>19</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H27" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I27" s="10"/>
+      <c r="I27" s="11"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
@@ -1043,7 +1058,7 @@
         <v>5.3578000000000001E-2</v>
       </c>
       <c r="K30">
-        <f t="shared" ref="K30:K33" si="6">B30-G30</f>
+        <f t="shared" ref="K30:K31" si="6">B30-G30</f>
         <v>-0.31999999999999995</v>
       </c>
       <c r="L30">
@@ -1230,10 +1245,10 @@
       <c r="A35" t="s">
         <v>11</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="10"/>
+      <c r="C35" s="11"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
@@ -1265,10 +1280,10 @@
       <c r="G37" t="s">
         <v>19</v>
       </c>
-      <c r="H37" s="10" t="s">
+      <c r="H37" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I37" s="10"/>
+      <c r="I37" s="11"/>
       <c r="K37" t="s">
         <v>17</v>
       </c>
@@ -1393,10 +1408,10 @@
       <c r="A42" t="s">
         <v>12</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="10"/>
+      <c r="C42" s="11"/>
       <c r="F42" t="s">
         <v>18</v>
       </c>
@@ -1674,6 +1689,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="H37:I37"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="L4:M4"/>
@@ -1683,11 +1703,391 @@
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="F3:G3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D80FCB69-8B09-6044-9387-7F999398C598}">
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="7.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="B2">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7">
+        <v>3.1275900000000002E-2</v>
+      </c>
+      <c r="C6" s="7">
+        <v>6.3664400000000001E-3</v>
+      </c>
+      <c r="D6" s="7">
+        <f>B6/$A$2</f>
+        <v>0.41701200000000005</v>
+      </c>
+      <c r="E6" s="7">
+        <f>D6*SQRT((C6/B6)^2+($B$2/$A$2)^2)</f>
+        <v>8.7751104992249029E-2</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7">
+        <v>2.8006300000000001E-2</v>
+      </c>
+      <c r="C7" s="7">
+        <v>5.4395199999999998E-3</v>
+      </c>
+      <c r="D7" s="7">
+        <f t="shared" ref="D7:D9" si="0">B7/$A$2</f>
+        <v>0.37341733333333338</v>
+      </c>
+      <c r="E7" s="7">
+        <f t="shared" ref="E7:E9" si="1">D7*SQRT((C7/B7)^2+($B$2/$A$2)^2)</f>
+        <v>7.5211613651368664E-2</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="7">
+        <v>4.5992999999999999E-2</v>
+      </c>
+      <c r="C8" s="7">
+        <v>4.4818899999999997E-3</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="0"/>
+        <v>0.61324000000000001</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="1"/>
+        <v>6.8123222646678194E-2</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="7">
+        <v>3.2809499999999998E-2</v>
+      </c>
+      <c r="C9" s="7">
+        <v>3.9320300000000004E-3</v>
+      </c>
+      <c r="D9" s="7">
+        <f t="shared" si="0"/>
+        <v>0.43746000000000002</v>
+      </c>
+      <c r="E9" s="7">
+        <f t="shared" si="1"/>
+        <v>5.7384163431308408E-2</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="7">
+        <v>4.3857500000000001E-2</v>
+      </c>
+      <c r="C13" s="7">
+        <v>8.7930500000000002E-3</v>
+      </c>
+      <c r="D13" s="7">
+        <f>B13/$A$2</f>
+        <v>0.58476666666666666</v>
+      </c>
+      <c r="E13" s="7">
+        <f>D13*SQRT((C13/B13)^2+($B$2/$A$2)^2)</f>
+        <v>0.12131791929461744</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7">
+        <v>2.55541E-2</v>
+      </c>
+      <c r="C14" s="7">
+        <v>7.5070299999999996E-3</v>
+      </c>
+      <c r="D14" s="7">
+        <f t="shared" ref="D14:D16" si="2">B14/$A$2</f>
+        <v>0.34072133333333332</v>
+      </c>
+      <c r="E14" s="7">
+        <f t="shared" ref="E14:E16" si="3">D14*SQRT((C14/B14)^2+($B$2/$A$2)^2)</f>
+        <v>0.10172988709996475</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="7">
+        <v>4.81976E-2</v>
+      </c>
+      <c r="C15" s="7">
+        <v>6.1603500000000002E-3</v>
+      </c>
+      <c r="D15" s="7">
+        <f t="shared" si="2"/>
+        <v>0.64263466666666669</v>
+      </c>
+      <c r="E15" s="7">
+        <f t="shared" si="3"/>
+        <v>8.9001953695738573E-2</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="7">
+        <v>3.4759999999999999E-2</v>
+      </c>
+      <c r="C16" s="7">
+        <v>5.4018699999999996E-3</v>
+      </c>
+      <c r="D16" s="7">
+        <f t="shared" si="2"/>
+        <v>0.46346666666666669</v>
+      </c>
+      <c r="E16" s="7">
+        <f t="shared" si="3"/>
+        <v>7.614841778722832E-2</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="10"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" s="7">
+        <v>1.7494300000000001E-2</v>
+      </c>
+      <c r="C20" s="7">
+        <v>9.2297200000000003E-3</v>
+      </c>
+      <c r="D20" s="7">
+        <f>B20/$A$2</f>
+        <v>0.23325733333333334</v>
+      </c>
+      <c r="E20" s="7">
+        <f>D20*SQRT((C20/B20)^2+($B$2/$A$2)^2)</f>
+        <v>0.12369013255551897</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" s="7">
+        <v>3.0685E-2</v>
+      </c>
+      <c r="C21" s="7">
+        <v>7.8925499999999999E-3</v>
+      </c>
+      <c r="D21" s="7">
+        <f t="shared" ref="D21:D23" si="4">B21/$A$2</f>
+        <v>0.40913333333333335</v>
+      </c>
+      <c r="E21" s="7">
+        <f t="shared" ref="E21:E23" si="5">D21*SQRT((C21/B21)^2+($B$2/$A$2)^2)</f>
+        <v>0.10747244554653575</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="7">
+        <v>4.3543699999999998E-2</v>
+      </c>
+      <c r="C22" s="7">
+        <v>6.5324700000000003E-3</v>
+      </c>
+      <c r="D22" s="7">
+        <f t="shared" si="4"/>
+        <v>0.58058266666666669</v>
+      </c>
+      <c r="E22" s="7">
+        <f t="shared" si="5"/>
+        <v>9.2439899058784691E-2</v>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="7">
+        <v>3.0622400000000001E-2</v>
+      </c>
+      <c r="C23" s="7">
+        <v>5.7343999999999997E-3</v>
+      </c>
+      <c r="D23" s="7">
+        <f t="shared" si="4"/>
+        <v>0.4082986666666667</v>
+      </c>
+      <c r="E23" s="7">
+        <f t="shared" si="5"/>
+        <v>7.9499174759354516E-2</v>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="B4:C4"/>
     <mergeCell ref="D4:E4"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="F4:G4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Sheets/SimulataneousFitResultsThesis.xlsx
+++ b/Sheets/SimulataneousFitResultsThesis.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10911"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samuelgrant/Documents/gm2/EDM/Sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE2A1F3-F7BD-D243-B399-37F7F3C128A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69095AC6-2D92-9A41-BC8E-41BDB935F306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="500" windowWidth="23580" windowHeight="16940" activeTab="1" xr2:uid="{17D71C46-F216-1347-8A90-14C7EE0E0845}"/>
+    <workbookView xWindow="-2900" yWindow="-20060" windowWidth="23580" windowHeight="16940" activeTab="2" xr2:uid="{17D71C46-F216-1347-8A90-14C7EE0E0845}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="SimultaneousFits" sheetId="2" r:id="rId2"/>
+    <sheet name="Note" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="37">
   <si>
     <t>d_EDM</t>
   </si>
@@ -114,6 +115,39 @@
   </si>
   <si>
     <t>d_EDM (S12S18)</t>
+  </si>
+  <si>
+    <t>chi2ndf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A_EDM^{BLIND} [mrad]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A_{g-2} [mrad]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> c [mrad]</t>
+  </si>
+  <si>
+    <t>Station</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> value</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> error</t>
+  </si>
+  <si>
+    <t>delta_rest</t>
+  </si>
+  <si>
+    <t>gamma</t>
+  </si>
+  <si>
+    <t>a_mu</t>
+  </si>
+  <si>
+    <t>delta_lab</t>
   </si>
 </sst>
 </file>
@@ -1689,11 +1723,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="H37:I37"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="L4:M4"/>
@@ -1703,6 +1732,11 @@
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B4:C4"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="H37:I37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2091,4 +2125,541 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0940890-2326-A847-8B67-0C5BE5C82FC0}">
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="2">
+        <v>1.1659208900000001E-3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2">
+        <f>SQRT(1+(1/B1))</f>
+        <v>29.303431969091314</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3">
+        <f>0.0495092*1000</f>
+        <v>49.5092</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4">
+        <f>B3/B2</f>
+        <v>1.6895358895920907</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>0.88305</v>
+      </c>
+      <c r="C9">
+        <v>4.3860099999999999E-2</v>
+      </c>
+      <c r="D9">
+        <v>8.7929400000000008E-3</v>
+      </c>
+      <c r="E9">
+        <v>-1.2127800000000001E-3</v>
+      </c>
+      <c r="F9">
+        <v>8.7887799999999995E-3</v>
+      </c>
+      <c r="G9">
+        <v>-1.1474600000000001E-3</v>
+      </c>
+      <c r="H9">
+        <v>6.2268699999999998E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
+        <v>0.85123700000000002</v>
+      </c>
+      <c r="C10">
+        <v>1.7480800000000001E-2</v>
+      </c>
+      <c r="D10">
+        <v>9.2295699999999994E-3</v>
+      </c>
+      <c r="E10">
+        <v>5.1927800000000001E-3</v>
+      </c>
+      <c r="F10">
+        <v>9.2193299999999995E-3</v>
+      </c>
+      <c r="G10">
+        <v>-2.07744E-4</v>
+      </c>
+      <c r="H10">
+        <v>6.5330099999999997E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>0.86763999999999997</v>
+      </c>
+      <c r="C11">
+        <v>3.1270800000000001E-2</v>
+      </c>
+      <c r="D11">
+        <v>6.3663499999999998E-3</v>
+      </c>
+      <c r="E11">
+        <v>1.8536099999999999E-3</v>
+      </c>
+      <c r="F11">
+        <v>6.3613899999999998E-3</v>
+      </c>
+      <c r="G11">
+        <v>-6.9955699999999996E-4</v>
+      </c>
+      <c r="H11">
+        <v>4.5074199999999998E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16">
+        <v>0.57067699999999999</v>
+      </c>
+      <c r="C16">
+        <v>2.5560300000000001E-2</v>
+      </c>
+      <c r="D16">
+        <v>7.5069000000000004E-3</v>
+      </c>
+      <c r="E16">
+        <v>-2.0172499999999999E-3</v>
+      </c>
+      <c r="F16">
+        <v>7.49178E-3</v>
+      </c>
+      <c r="G16">
+        <v>-2.2965899999999998E-3</v>
+      </c>
+      <c r="H16">
+        <v>5.3120900000000002E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17">
+        <v>0.82675100000000001</v>
+      </c>
+      <c r="C17">
+        <v>3.0718100000000002E-2</v>
+      </c>
+      <c r="D17">
+        <v>7.8924200000000007E-3</v>
+      </c>
+      <c r="E17">
+        <v>-1.01289E-2</v>
+      </c>
+      <c r="F17">
+        <v>7.88698E-3</v>
+      </c>
+      <c r="G17">
+        <v>-1.81909E-3</v>
+      </c>
+      <c r="H17">
+        <v>5.5873600000000004E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18">
+        <v>0.69826999999999995</v>
+      </c>
+      <c r="C18">
+        <v>2.80253E-2</v>
+      </c>
+      <c r="D18">
+        <v>5.4394300000000003E-3</v>
+      </c>
+      <c r="E18">
+        <v>-5.8769399999999998E-3</v>
+      </c>
+      <c r="F18">
+        <v>5.4318600000000002E-3</v>
+      </c>
+      <c r="G18">
+        <v>-2.06347E-3</v>
+      </c>
+      <c r="H18">
+        <v>3.84987E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>1.0548599999999999</v>
+      </c>
+      <c r="C23">
+        <v>4.8196799999999998E-2</v>
+      </c>
+      <c r="D23">
+        <v>6.1602799999999997E-3</v>
+      </c>
+      <c r="E23">
+        <v>4.0131699999999999E-4</v>
+      </c>
+      <c r="F23">
+        <v>6.1536000000000004E-3</v>
+      </c>
+      <c r="G23">
+        <v>3.6478299999999999E-3</v>
+      </c>
+      <c r="H23">
+        <v>4.3609800000000004E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24">
+        <v>1.4328399999999999</v>
+      </c>
+      <c r="C24">
+        <v>4.3546599999999998E-2</v>
+      </c>
+      <c r="D24">
+        <v>6.53238E-3</v>
+      </c>
+      <c r="E24">
+        <v>-2.7177899999999999E-3</v>
+      </c>
+      <c r="F24">
+        <v>6.5260400000000003E-3</v>
+      </c>
+      <c r="G24">
+        <v>4.2183400000000001E-3</v>
+      </c>
+      <c r="H24">
+        <v>4.62364E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25">
+        <v>1.4193199999999999</v>
+      </c>
+      <c r="C25">
+        <v>4.5993899999999997E-2</v>
+      </c>
+      <c r="D25">
+        <v>4.48183E-3</v>
+      </c>
+      <c r="E25">
+        <v>-1.07424E-3</v>
+      </c>
+      <c r="F25">
+        <v>4.47716E-3</v>
+      </c>
+      <c r="G25">
+        <v>3.9147299999999999E-3</v>
+      </c>
+      <c r="H25">
+        <v>3.1725099999999999E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" t="s">
+        <v>31</v>
+      </c>
+      <c r="D29" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" t="s">
+        <v>31</v>
+      </c>
+      <c r="F29" t="s">
+        <v>32</v>
+      </c>
+      <c r="G29" t="s">
+        <v>31</v>
+      </c>
+      <c r="H29" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30">
+        <v>0.77335799999999999</v>
+      </c>
+      <c r="C30">
+        <v>3.4760399999999997E-2</v>
+      </c>
+      <c r="D30">
+        <v>5.4018099999999999E-3</v>
+      </c>
+      <c r="E30">
+        <v>7.9582899999999998E-3</v>
+      </c>
+      <c r="F30">
+        <v>5.3944500000000003E-3</v>
+      </c>
+      <c r="G30">
+        <v>1.65763E-3</v>
+      </c>
+      <c r="H30">
+        <v>3.8233299999999998E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31">
+        <v>0.46556700000000001</v>
+      </c>
+      <c r="C31">
+        <v>3.0622099999999999E-2</v>
+      </c>
+      <c r="D31">
+        <v>5.7343400000000001E-3</v>
+      </c>
+      <c r="E31" s="2">
+        <v>-7.1671299999999999E-6</v>
+      </c>
+      <c r="F31">
+        <v>5.7283000000000004E-3</v>
+      </c>
+      <c r="G31">
+        <v>-1.49455E-4</v>
+      </c>
+      <c r="H31">
+        <v>4.0587699999999997E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32">
+        <v>0.62349500000000002</v>
+      </c>
+      <c r="C32">
+        <v>3.2809499999999998E-2</v>
+      </c>
+      <c r="D32">
+        <v>3.9319899999999998E-3</v>
+      </c>
+      <c r="E32">
+        <v>4.2053200000000002E-3</v>
+      </c>
+      <c r="F32">
+        <v>3.9272200000000004E-3</v>
+      </c>
+      <c r="G32">
+        <v>8.0419499999999995E-4</v>
+      </c>
+      <c r="H32">
+        <v>2.7830400000000001E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>